--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/_Копия дв 201026 лгрсч ост сыр (Чепрасова).xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/_Копия дв 201026 лгрсч ост сыр (Чепрасова).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Владелец\Desktop\Заказы ЛП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456EA62B-2E97-4666-8D8E-32784A162294}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8784"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$40</definedName>
   </definedNames>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -298,7 +307,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
@@ -451,7 +460,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Arial10px" xfId="1"/>
+    <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -751,32 +760,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AY498"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
-    <col min="3" max="4" width="6" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="7" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="6" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="5" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="1" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="7" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="0.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="7" hidden="1" customWidth="1"/>
-    <col min="16" max="19" width="7" customWidth="1"/>
+    <col min="3" max="4" width="6" customWidth="1"/>
+    <col min="5" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="5" style="6" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="10" max="10" width="1" customWidth="1"/>
+    <col min="11" max="12" width="7" customWidth="1"/>
+    <col min="13" max="14" width="0.42578125" customWidth="1"/>
+    <col min="15" max="19" width="7" customWidth="1"/>
     <col min="20" max="20" width="7" style="12" customWidth="1"/>
     <col min="21" max="22" width="5" customWidth="1"/>
     <col min="23" max="32" width="6" customWidth="1"/>
-    <col min="33" max="33" width="20.6640625" style="12" customWidth="1"/>
-    <col min="34" max="34" width="42.44140625" customWidth="1"/>
+    <col min="33" max="33" width="20.7109375" style="12" customWidth="1"/>
+    <col min="34" max="34" width="42.42578125" customWidth="1"/>
     <col min="35" max="35" width="7" customWidth="1"/>
     <col min="36" max="51" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -829,7 +837,7 @@
       <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -884,7 +892,7 @@
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1003,7 +1011,7 @@
       <c r="AX3" s="1"/>
       <c r="AY3" s="1"/>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1084,7 +1092,7 @@
       <c r="AX4" s="1"/>
       <c r="AY4" s="1"/>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1102,7 +1110,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="4">
-        <f t="shared" ref="K5:S5" si="0">SUM(K6:K498)</f>
+        <f t="shared" ref="K5:T5" si="0">SUM(K6:K498)</f>
         <v>1819.1999999999998</v>
       </c>
       <c r="L5" s="4">
@@ -1137,7 +1145,10 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="T5" s="4"/>
+      <c r="T5" s="4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="4">
@@ -1203,7 +1214,7 @@
       <c r="AX5" s="1"/>
       <c r="AY5" s="1"/>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -1311,7 +1322,7 @@
       <c r="AX6" s="1"/>
       <c r="AY6" s="1"/>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -1418,7 +1429,7 @@
       <c r="AX7" s="1"/>
       <c r="AY7" s="1"/>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -1525,7 +1536,7 @@
       <c r="AX8" s="1"/>
       <c r="AY8" s="1"/>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -1641,7 +1652,7 @@
       <c r="AX9" s="1"/>
       <c r="AY9" s="1"/>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
@@ -1747,7 +1758,7 @@
       <c r="AX10" s="1"/>
       <c r="AY10" s="1"/>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
@@ -1847,7 +1858,7 @@
       <c r="AX11" s="1"/>
       <c r="AY11" s="1"/>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
@@ -1953,7 +1964,7 @@
       <c r="AX12" s="1"/>
       <c r="AY12" s="1"/>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
@@ -2057,7 +2068,7 @@
       <c r="AX13" s="1"/>
       <c r="AY13" s="1"/>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -2166,7 +2177,7 @@
       <c r="AX14" s="1"/>
       <c r="AY14" s="1"/>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>49</v>
       </c>
@@ -2274,7 +2285,7 @@
       <c r="AX15" s="1"/>
       <c r="AY15" s="1"/>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -2381,7 +2392,7 @@
       <c r="AX16" s="1"/>
       <c r="AY16" s="1"/>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
@@ -2491,7 +2502,7 @@
       <c r="AX17" s="1"/>
       <c r="AY17" s="1"/>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -2602,7 +2613,7 @@
       <c r="AX18" s="1"/>
       <c r="AY18" s="1"/>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>53</v>
       </c>
@@ -2708,7 +2719,7 @@
       <c r="AX19" s="1"/>
       <c r="AY19" s="1"/>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>54</v>
       </c>
@@ -2814,7 +2825,7 @@
       <c r="AX20" s="1"/>
       <c r="AY20" s="1"/>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
@@ -2920,7 +2931,7 @@
       <c r="AX21" s="1"/>
       <c r="AY21" s="1"/>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
@@ -3026,7 +3037,7 @@
       <c r="AX22" s="1"/>
       <c r="AY22" s="1"/>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -3139,7 +3150,7 @@
       <c r="AX23" s="1"/>
       <c r="AY23" s="1"/>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>59</v>
       </c>
@@ -3250,7 +3261,7 @@
       <c r="AX24" s="1"/>
       <c r="AY24" s="1"/>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>60</v>
       </c>
@@ -3359,7 +3370,7 @@
       <c r="AX25" s="1"/>
       <c r="AY25" s="1"/>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>61</v>
       </c>
@@ -3467,7 +3478,7 @@
       <c r="AX26" s="1"/>
       <c r="AY26" s="1"/>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>62</v>
       </c>
@@ -3578,7 +3589,7 @@
       <c r="AX27" s="1"/>
       <c r="AY27" s="1"/>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>63</v>
       </c>
@@ -3689,7 +3700,7 @@
       <c r="AX28" s="1"/>
       <c r="AY28" s="1"/>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>64</v>
       </c>
@@ -3793,7 +3804,7 @@
       <c r="AX29" s="1"/>
       <c r="AY29" s="1"/>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -3901,7 +3912,7 @@
       <c r="AX30" s="1"/>
       <c r="AY30" s="1"/>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>66</v>
       </c>
@@ -4008,7 +4019,7 @@
       <c r="AX31" s="1"/>
       <c r="AY31" s="1"/>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>67</v>
       </c>
@@ -4114,7 +4125,7 @@
       <c r="AX32" s="1"/>
       <c r="AY32" s="1"/>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>68</v>
       </c>
@@ -4221,7 +4232,7 @@
       <c r="AX33" s="1"/>
       <c r="AY33" s="1"/>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>69</v>
       </c>
@@ -4334,7 +4345,7 @@
       <c r="AX34" s="1"/>
       <c r="AY34" s="1"/>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>71</v>
       </c>
@@ -4443,7 +4454,7 @@
       <c r="AX35" s="1"/>
       <c r="AY35" s="1"/>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>72</v>
       </c>
@@ -4554,7 +4565,7 @@
       <c r="AX36" s="1"/>
       <c r="AY36" s="1"/>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -4665,7 +4676,7 @@
       <c r="AX37" s="1"/>
       <c r="AY37" s="1"/>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -4772,7 +4783,7 @@
       <c r="AX38" s="1"/>
       <c r="AY38" s="1"/>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>75</v>
       </c>
@@ -4880,7 +4891,7 @@
       <c r="AX39" s="1"/>
       <c r="AY39" s="1"/>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>76</v>
       </c>
@@ -4986,7 +4997,7 @@
       <c r="AX40" s="1"/>
       <c r="AY40" s="1"/>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -5039,7 +5050,7 @@
       <c r="AX41" s="1"/>
       <c r="AY41" s="1"/>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -5092,7 +5103,7 @@
       <c r="AX42" s="1"/>
       <c r="AY42" s="1"/>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -5145,7 +5156,7 @@
       <c r="AX43" s="1"/>
       <c r="AY43" s="1"/>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -5198,7 +5209,7 @@
       <c r="AX44" s="1"/>
       <c r="AY44" s="1"/>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -5251,7 +5262,7 @@
       <c r="AX45" s="1"/>
       <c r="AY45" s="1"/>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -5304,7 +5315,7 @@
       <c r="AX46" s="1"/>
       <c r="AY46" s="1"/>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -5357,7 +5368,7 @@
       <c r="AX47" s="1"/>
       <c r="AY47" s="1"/>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -5410,7 +5421,7 @@
       <c r="AX48" s="1"/>
       <c r="AY48" s="1"/>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -5463,7 +5474,7 @@
       <c r="AX49" s="1"/>
       <c r="AY49" s="1"/>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -5516,7 +5527,7 @@
       <c r="AX50" s="1"/>
       <c r="AY50" s="1"/>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -5569,7 +5580,7 @@
       <c r="AX51" s="1"/>
       <c r="AY51" s="1"/>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -5622,7 +5633,7 @@
       <c r="AX52" s="1"/>
       <c r="AY52" s="1"/>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -5675,7 +5686,7 @@
       <c r="AX53" s="1"/>
       <c r="AY53" s="1"/>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -5728,7 +5739,7 @@
       <c r="AX54" s="1"/>
       <c r="AY54" s="1"/>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -5781,7 +5792,7 @@
       <c r="AX55" s="1"/>
       <c r="AY55" s="1"/>
     </row>
-    <row r="56" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -5834,7 +5845,7 @@
       <c r="AX56" s="1"/>
       <c r="AY56" s="1"/>
     </row>
-    <row r="57" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -5887,7 +5898,7 @@
       <c r="AX57" s="1"/>
       <c r="AY57" s="1"/>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -5940,7 +5951,7 @@
       <c r="AX58" s="1"/>
       <c r="AY58" s="1"/>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -5993,7 +6004,7 @@
       <c r="AX59" s="1"/>
       <c r="AY59" s="1"/>
     </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -6046,7 +6057,7 @@
       <c r="AX60" s="1"/>
       <c r="AY60" s="1"/>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -6099,7 +6110,7 @@
       <c r="AX61" s="1"/>
       <c r="AY61" s="1"/>
     </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -6152,7 +6163,7 @@
       <c r="AX62" s="1"/>
       <c r="AY62" s="1"/>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -6205,7 +6216,7 @@
       <c r="AX63" s="1"/>
       <c r="AY63" s="1"/>
     </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -6258,7 +6269,7 @@
       <c r="AX64" s="1"/>
       <c r="AY64" s="1"/>
     </row>
-    <row r="65" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -6311,7 +6322,7 @@
       <c r="AX65" s="1"/>
       <c r="AY65" s="1"/>
     </row>
-    <row r="66" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -6364,7 +6375,7 @@
       <c r="AX66" s="1"/>
       <c r="AY66" s="1"/>
     </row>
-    <row r="67" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -6417,7 +6428,7 @@
       <c r="AX67" s="1"/>
       <c r="AY67" s="1"/>
     </row>
-    <row r="68" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -6470,7 +6481,7 @@
       <c r="AX68" s="1"/>
       <c r="AY68" s="1"/>
     </row>
-    <row r="69" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -6523,7 +6534,7 @@
       <c r="AX69" s="1"/>
       <c r="AY69" s="1"/>
     </row>
-    <row r="70" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -6576,7 +6587,7 @@
       <c r="AX70" s="1"/>
       <c r="AY70" s="1"/>
     </row>
-    <row r="71" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -6629,7 +6640,7 @@
       <c r="AX71" s="1"/>
       <c r="AY71" s="1"/>
     </row>
-    <row r="72" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -6682,7 +6693,7 @@
       <c r="AX72" s="1"/>
       <c r="AY72" s="1"/>
     </row>
-    <row r="73" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -6735,7 +6746,7 @@
       <c r="AX73" s="1"/>
       <c r="AY73" s="1"/>
     </row>
-    <row r="74" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -6788,7 +6799,7 @@
       <c r="AX74" s="1"/>
       <c r="AY74" s="1"/>
     </row>
-    <row r="75" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -6841,7 +6852,7 @@
       <c r="AX75" s="1"/>
       <c r="AY75" s="1"/>
     </row>
-    <row r="76" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -6894,7 +6905,7 @@
       <c r="AX76" s="1"/>
       <c r="AY76" s="1"/>
     </row>
-    <row r="77" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -6947,7 +6958,7 @@
       <c r="AX77" s="1"/>
       <c r="AY77" s="1"/>
     </row>
-    <row r="78" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -7000,7 +7011,7 @@
       <c r="AX78" s="1"/>
       <c r="AY78" s="1"/>
     </row>
-    <row r="79" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -7053,7 +7064,7 @@
       <c r="AX79" s="1"/>
       <c r="AY79" s="1"/>
     </row>
-    <row r="80" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -7106,7 +7117,7 @@
       <c r="AX80" s="1"/>
       <c r="AY80" s="1"/>
     </row>
-    <row r="81" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -7159,7 +7170,7 @@
       <c r="AX81" s="1"/>
       <c r="AY81" s="1"/>
     </row>
-    <row r="82" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7212,7 +7223,7 @@
       <c r="AX82" s="1"/>
       <c r="AY82" s="1"/>
     </row>
-    <row r="83" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7265,7 +7276,7 @@
       <c r="AX83" s="1"/>
       <c r="AY83" s="1"/>
     </row>
-    <row r="84" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7318,7 +7329,7 @@
       <c r="AX84" s="1"/>
       <c r="AY84" s="1"/>
     </row>
-    <row r="85" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7371,7 +7382,7 @@
       <c r="AX85" s="1"/>
       <c r="AY85" s="1"/>
     </row>
-    <row r="86" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7424,7 +7435,7 @@
       <c r="AX86" s="1"/>
       <c r="AY86" s="1"/>
     </row>
-    <row r="87" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7477,7 +7488,7 @@
       <c r="AX87" s="1"/>
       <c r="AY87" s="1"/>
     </row>
-    <row r="88" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7530,7 +7541,7 @@
       <c r="AX88" s="1"/>
       <c r="AY88" s="1"/>
     </row>
-    <row r="89" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7583,7 +7594,7 @@
       <c r="AX89" s="1"/>
       <c r="AY89" s="1"/>
     </row>
-    <row r="90" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7636,7 +7647,7 @@
       <c r="AX90" s="1"/>
       <c r="AY90" s="1"/>
     </row>
-    <row r="91" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7689,7 +7700,7 @@
       <c r="AX91" s="1"/>
       <c r="AY91" s="1"/>
     </row>
-    <row r="92" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7742,7 +7753,7 @@
       <c r="AX92" s="1"/>
       <c r="AY92" s="1"/>
     </row>
-    <row r="93" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7795,7 +7806,7 @@
       <c r="AX93" s="1"/>
       <c r="AY93" s="1"/>
     </row>
-    <row r="94" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7848,7 +7859,7 @@
       <c r="AX94" s="1"/>
       <c r="AY94" s="1"/>
     </row>
-    <row r="95" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7901,7 +7912,7 @@
       <c r="AX95" s="1"/>
       <c r="AY95" s="1"/>
     </row>
-    <row r="96" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7954,7 +7965,7 @@
       <c r="AX96" s="1"/>
       <c r="AY96" s="1"/>
     </row>
-    <row r="97" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -8007,7 +8018,7 @@
       <c r="AX97" s="1"/>
       <c r="AY97" s="1"/>
     </row>
-    <row r="98" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -8060,7 +8071,7 @@
       <c r="AX98" s="1"/>
       <c r="AY98" s="1"/>
     </row>
-    <row r="99" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -8113,7 +8124,7 @@
       <c r="AX99" s="1"/>
       <c r="AY99" s="1"/>
     </row>
-    <row r="100" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -8166,7 +8177,7 @@
       <c r="AX100" s="1"/>
       <c r="AY100" s="1"/>
     </row>
-    <row r="101" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -8219,7 +8230,7 @@
       <c r="AX101" s="1"/>
       <c r="AY101" s="1"/>
     </row>
-    <row r="102" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -8272,7 +8283,7 @@
       <c r="AX102" s="1"/>
       <c r="AY102" s="1"/>
     </row>
-    <row r="103" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -8325,7 +8336,7 @@
       <c r="AX103" s="1"/>
       <c r="AY103" s="1"/>
     </row>
-    <row r="104" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -8378,7 +8389,7 @@
       <c r="AX104" s="1"/>
       <c r="AY104" s="1"/>
     </row>
-    <row r="105" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -8431,7 +8442,7 @@
       <c r="AX105" s="1"/>
       <c r="AY105" s="1"/>
     </row>
-    <row r="106" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -8484,7 +8495,7 @@
       <c r="AX106" s="1"/>
       <c r="AY106" s="1"/>
     </row>
-    <row r="107" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -8537,7 +8548,7 @@
       <c r="AX107" s="1"/>
       <c r="AY107" s="1"/>
     </row>
-    <row r="108" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -8590,7 +8601,7 @@
       <c r="AX108" s="1"/>
       <c r="AY108" s="1"/>
     </row>
-    <row r="109" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -8643,7 +8654,7 @@
       <c r="AX109" s="1"/>
       <c r="AY109" s="1"/>
     </row>
-    <row r="110" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -8696,7 +8707,7 @@
       <c r="AX110" s="1"/>
       <c r="AY110" s="1"/>
     </row>
-    <row r="111" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -8749,7 +8760,7 @@
       <c r="AX111" s="1"/>
       <c r="AY111" s="1"/>
     </row>
-    <row r="112" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -8802,7 +8813,7 @@
       <c r="AX112" s="1"/>
       <c r="AY112" s="1"/>
     </row>
-    <row r="113" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -8855,7 +8866,7 @@
       <c r="AX113" s="1"/>
       <c r="AY113" s="1"/>
     </row>
-    <row r="114" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -8908,7 +8919,7 @@
       <c r="AX114" s="1"/>
       <c r="AY114" s="1"/>
     </row>
-    <row r="115" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -8961,7 +8972,7 @@
       <c r="AX115" s="1"/>
       <c r="AY115" s="1"/>
     </row>
-    <row r="116" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -9014,7 +9025,7 @@
       <c r="AX116" s="1"/>
       <c r="AY116" s="1"/>
     </row>
-    <row r="117" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -9067,7 +9078,7 @@
       <c r="AX117" s="1"/>
       <c r="AY117" s="1"/>
     </row>
-    <row r="118" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -9120,7 +9131,7 @@
       <c r="AX118" s="1"/>
       <c r="AY118" s="1"/>
     </row>
-    <row r="119" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -9173,7 +9184,7 @@
       <c r="AX119" s="1"/>
       <c r="AY119" s="1"/>
     </row>
-    <row r="120" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -9226,7 +9237,7 @@
       <c r="AX120" s="1"/>
       <c r="AY120" s="1"/>
     </row>
-    <row r="121" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -9279,7 +9290,7 @@
       <c r="AX121" s="1"/>
       <c r="AY121" s="1"/>
     </row>
-    <row r="122" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -9332,7 +9343,7 @@
       <c r="AX122" s="1"/>
       <c r="AY122" s="1"/>
     </row>
-    <row r="123" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -9385,7 +9396,7 @@
       <c r="AX123" s="1"/>
       <c r="AY123" s="1"/>
     </row>
-    <row r="124" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -9438,7 +9449,7 @@
       <c r="AX124" s="1"/>
       <c r="AY124" s="1"/>
     </row>
-    <row r="125" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -9491,7 +9502,7 @@
       <c r="AX125" s="1"/>
       <c r="AY125" s="1"/>
     </row>
-    <row r="126" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -9544,7 +9555,7 @@
       <c r="AX126" s="1"/>
       <c r="AY126" s="1"/>
     </row>
-    <row r="127" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -9597,7 +9608,7 @@
       <c r="AX127" s="1"/>
       <c r="AY127" s="1"/>
     </row>
-    <row r="128" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -9650,7 +9661,7 @@
       <c r="AX128" s="1"/>
       <c r="AY128" s="1"/>
     </row>
-    <row r="129" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -9703,7 +9714,7 @@
       <c r="AX129" s="1"/>
       <c r="AY129" s="1"/>
     </row>
-    <row r="130" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -9756,7 +9767,7 @@
       <c r="AX130" s="1"/>
       <c r="AY130" s="1"/>
     </row>
-    <row r="131" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -9809,7 +9820,7 @@
       <c r="AX131" s="1"/>
       <c r="AY131" s="1"/>
     </row>
-    <row r="132" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -9862,7 +9873,7 @@
       <c r="AX132" s="1"/>
       <c r="AY132" s="1"/>
     </row>
-    <row r="133" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -9915,7 +9926,7 @@
       <c r="AX133" s="1"/>
       <c r="AY133" s="1"/>
     </row>
-    <row r="134" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -9968,7 +9979,7 @@
       <c r="AX134" s="1"/>
       <c r="AY134" s="1"/>
     </row>
-    <row r="135" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -10021,7 +10032,7 @@
       <c r="AX135" s="1"/>
       <c r="AY135" s="1"/>
     </row>
-    <row r="136" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -10074,7 +10085,7 @@
       <c r="AX136" s="1"/>
       <c r="AY136" s="1"/>
     </row>
-    <row r="137" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -10127,7 +10138,7 @@
       <c r="AX137" s="1"/>
       <c r="AY137" s="1"/>
     </row>
-    <row r="138" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -10180,7 +10191,7 @@
       <c r="AX138" s="1"/>
       <c r="AY138" s="1"/>
     </row>
-    <row r="139" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -10233,7 +10244,7 @@
       <c r="AX139" s="1"/>
       <c r="AY139" s="1"/>
     </row>
-    <row r="140" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -10286,7 +10297,7 @@
       <c r="AX140" s="1"/>
       <c r="AY140" s="1"/>
     </row>
-    <row r="141" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -10339,7 +10350,7 @@
       <c r="AX141" s="1"/>
       <c r="AY141" s="1"/>
     </row>
-    <row r="142" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -10392,7 +10403,7 @@
       <c r="AX142" s="1"/>
       <c r="AY142" s="1"/>
     </row>
-    <row r="143" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -10445,7 +10456,7 @@
       <c r="AX143" s="1"/>
       <c r="AY143" s="1"/>
     </row>
-    <row r="144" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -10498,7 +10509,7 @@
       <c r="AX144" s="1"/>
       <c r="AY144" s="1"/>
     </row>
-    <row r="145" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -10551,7 +10562,7 @@
       <c r="AX145" s="1"/>
       <c r="AY145" s="1"/>
     </row>
-    <row r="146" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -10604,7 +10615,7 @@
       <c r="AX146" s="1"/>
       <c r="AY146" s="1"/>
     </row>
-    <row r="147" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -10657,7 +10668,7 @@
       <c r="AX147" s="1"/>
       <c r="AY147" s="1"/>
     </row>
-    <row r="148" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -10710,7 +10721,7 @@
       <c r="AX148" s="1"/>
       <c r="AY148" s="1"/>
     </row>
-    <row r="149" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -10763,7 +10774,7 @@
       <c r="AX149" s="1"/>
       <c r="AY149" s="1"/>
     </row>
-    <row r="150" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -10816,7 +10827,7 @@
       <c r="AX150" s="1"/>
       <c r="AY150" s="1"/>
     </row>
-    <row r="151" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -10869,7 +10880,7 @@
       <c r="AX151" s="1"/>
       <c r="AY151" s="1"/>
     </row>
-    <row r="152" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -10922,7 +10933,7 @@
       <c r="AX152" s="1"/>
       <c r="AY152" s="1"/>
     </row>
-    <row r="153" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -10975,7 +10986,7 @@
       <c r="AX153" s="1"/>
       <c r="AY153" s="1"/>
     </row>
-    <row r="154" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -11028,7 +11039,7 @@
       <c r="AX154" s="1"/>
       <c r="AY154" s="1"/>
     </row>
-    <row r="155" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -11081,7 +11092,7 @@
       <c r="AX155" s="1"/>
       <c r="AY155" s="1"/>
     </row>
-    <row r="156" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -11134,7 +11145,7 @@
       <c r="AX156" s="1"/>
       <c r="AY156" s="1"/>
     </row>
-    <row r="157" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -11187,7 +11198,7 @@
       <c r="AX157" s="1"/>
       <c r="AY157" s="1"/>
     </row>
-    <row r="158" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -11240,7 +11251,7 @@
       <c r="AX158" s="1"/>
       <c r="AY158" s="1"/>
     </row>
-    <row r="159" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -11293,7 +11304,7 @@
       <c r="AX159" s="1"/>
       <c r="AY159" s="1"/>
     </row>
-    <row r="160" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -11346,7 +11357,7 @@
       <c r="AX160" s="1"/>
       <c r="AY160" s="1"/>
     </row>
-    <row r="161" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -11399,7 +11410,7 @@
       <c r="AX161" s="1"/>
       <c r="AY161" s="1"/>
     </row>
-    <row r="162" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -11452,7 +11463,7 @@
       <c r="AX162" s="1"/>
       <c r="AY162" s="1"/>
     </row>
-    <row r="163" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -11505,7 +11516,7 @@
       <c r="AX163" s="1"/>
       <c r="AY163" s="1"/>
     </row>
-    <row r="164" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -11558,7 +11569,7 @@
       <c r="AX164" s="1"/>
       <c r="AY164" s="1"/>
     </row>
-    <row r="165" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -11611,7 +11622,7 @@
       <c r="AX165" s="1"/>
       <c r="AY165" s="1"/>
     </row>
-    <row r="166" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -11664,7 +11675,7 @@
       <c r="AX166" s="1"/>
       <c r="AY166" s="1"/>
     </row>
-    <row r="167" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -11717,7 +11728,7 @@
       <c r="AX167" s="1"/>
       <c r="AY167" s="1"/>
     </row>
-    <row r="168" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -11770,7 +11781,7 @@
       <c r="AX168" s="1"/>
       <c r="AY168" s="1"/>
     </row>
-    <row r="169" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -11823,7 +11834,7 @@
       <c r="AX169" s="1"/>
       <c r="AY169" s="1"/>
     </row>
-    <row r="170" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -11876,7 +11887,7 @@
       <c r="AX170" s="1"/>
       <c r="AY170" s="1"/>
     </row>
-    <row r="171" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -11929,7 +11940,7 @@
       <c r="AX171" s="1"/>
       <c r="AY171" s="1"/>
     </row>
-    <row r="172" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -11982,7 +11993,7 @@
       <c r="AX172" s="1"/>
       <c r="AY172" s="1"/>
     </row>
-    <row r="173" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -12035,7 +12046,7 @@
       <c r="AX173" s="1"/>
       <c r="AY173" s="1"/>
     </row>
-    <row r="174" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -12088,7 +12099,7 @@
       <c r="AX174" s="1"/>
       <c r="AY174" s="1"/>
     </row>
-    <row r="175" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -12141,7 +12152,7 @@
       <c r="AX175" s="1"/>
       <c r="AY175" s="1"/>
     </row>
-    <row r="176" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -12194,7 +12205,7 @@
       <c r="AX176" s="1"/>
       <c r="AY176" s="1"/>
     </row>
-    <row r="177" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -12247,7 +12258,7 @@
       <c r="AX177" s="1"/>
       <c r="AY177" s="1"/>
     </row>
-    <row r="178" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -12300,7 +12311,7 @@
       <c r="AX178" s="1"/>
       <c r="AY178" s="1"/>
     </row>
-    <row r="179" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -12353,7 +12364,7 @@
       <c r="AX179" s="1"/>
       <c r="AY179" s="1"/>
     </row>
-    <row r="180" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -12406,7 +12417,7 @@
       <c r="AX180" s="1"/>
       <c r="AY180" s="1"/>
     </row>
-    <row r="181" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -12459,7 +12470,7 @@
       <c r="AX181" s="1"/>
       <c r="AY181" s="1"/>
     </row>
-    <row r="182" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -12512,7 +12523,7 @@
       <c r="AX182" s="1"/>
       <c r="AY182" s="1"/>
     </row>
-    <row r="183" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -12565,7 +12576,7 @@
       <c r="AX183" s="1"/>
       <c r="AY183" s="1"/>
     </row>
-    <row r="184" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -12618,7 +12629,7 @@
       <c r="AX184" s="1"/>
       <c r="AY184" s="1"/>
     </row>
-    <row r="185" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -12671,7 +12682,7 @@
       <c r="AX185" s="1"/>
       <c r="AY185" s="1"/>
     </row>
-    <row r="186" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -12724,7 +12735,7 @@
       <c r="AX186" s="1"/>
       <c r="AY186" s="1"/>
     </row>
-    <row r="187" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -12777,7 +12788,7 @@
       <c r="AX187" s="1"/>
       <c r="AY187" s="1"/>
     </row>
-    <row r="188" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -12830,7 +12841,7 @@
       <c r="AX188" s="1"/>
       <c r="AY188" s="1"/>
     </row>
-    <row r="189" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -12883,7 +12894,7 @@
       <c r="AX189" s="1"/>
       <c r="AY189" s="1"/>
     </row>
-    <row r="190" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -12936,7 +12947,7 @@
       <c r="AX190" s="1"/>
       <c r="AY190" s="1"/>
     </row>
-    <row r="191" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -12989,7 +13000,7 @@
       <c r="AX191" s="1"/>
       <c r="AY191" s="1"/>
     </row>
-    <row r="192" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -13042,7 +13053,7 @@
       <c r="AX192" s="1"/>
       <c r="AY192" s="1"/>
     </row>
-    <row r="193" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -13095,7 +13106,7 @@
       <c r="AX193" s="1"/>
       <c r="AY193" s="1"/>
     </row>
-    <row r="194" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -13148,7 +13159,7 @@
       <c r="AX194" s="1"/>
       <c r="AY194" s="1"/>
     </row>
-    <row r="195" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -13201,7 +13212,7 @@
       <c r="AX195" s="1"/>
       <c r="AY195" s="1"/>
     </row>
-    <row r="196" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -13254,7 +13265,7 @@
       <c r="AX196" s="1"/>
       <c r="AY196" s="1"/>
     </row>
-    <row r="197" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -13307,7 +13318,7 @@
       <c r="AX197" s="1"/>
       <c r="AY197" s="1"/>
     </row>
-    <row r="198" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -13360,7 +13371,7 @@
       <c r="AX198" s="1"/>
       <c r="AY198" s="1"/>
     </row>
-    <row r="199" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -13413,7 +13424,7 @@
       <c r="AX199" s="1"/>
       <c r="AY199" s="1"/>
     </row>
-    <row r="200" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -13466,7 +13477,7 @@
       <c r="AX200" s="1"/>
       <c r="AY200" s="1"/>
     </row>
-    <row r="201" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -13519,7 +13530,7 @@
       <c r="AX201" s="1"/>
       <c r="AY201" s="1"/>
     </row>
-    <row r="202" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -13572,7 +13583,7 @@
       <c r="AX202" s="1"/>
       <c r="AY202" s="1"/>
     </row>
-    <row r="203" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -13625,7 +13636,7 @@
       <c r="AX203" s="1"/>
       <c r="AY203" s="1"/>
     </row>
-    <row r="204" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -13678,7 +13689,7 @@
       <c r="AX204" s="1"/>
       <c r="AY204" s="1"/>
     </row>
-    <row r="205" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -13731,7 +13742,7 @@
       <c r="AX205" s="1"/>
       <c r="AY205" s="1"/>
     </row>
-    <row r="206" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -13784,7 +13795,7 @@
       <c r="AX206" s="1"/>
       <c r="AY206" s="1"/>
     </row>
-    <row r="207" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -13837,7 +13848,7 @@
       <c r="AX207" s="1"/>
       <c r="AY207" s="1"/>
     </row>
-    <row r="208" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -13890,7 +13901,7 @@
       <c r="AX208" s="1"/>
       <c r="AY208" s="1"/>
     </row>
-    <row r="209" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -13943,7 +13954,7 @@
       <c r="AX209" s="1"/>
       <c r="AY209" s="1"/>
     </row>
-    <row r="210" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -13996,7 +14007,7 @@
       <c r="AX210" s="1"/>
       <c r="AY210" s="1"/>
     </row>
-    <row r="211" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -14049,7 +14060,7 @@
       <c r="AX211" s="1"/>
       <c r="AY211" s="1"/>
     </row>
-    <row r="212" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -14102,7 +14113,7 @@
       <c r="AX212" s="1"/>
       <c r="AY212" s="1"/>
     </row>
-    <row r="213" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -14155,7 +14166,7 @@
       <c r="AX213" s="1"/>
       <c r="AY213" s="1"/>
     </row>
-    <row r="214" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -14208,7 +14219,7 @@
       <c r="AX214" s="1"/>
       <c r="AY214" s="1"/>
     </row>
-    <row r="215" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -14261,7 +14272,7 @@
       <c r="AX215" s="1"/>
       <c r="AY215" s="1"/>
     </row>
-    <row r="216" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -14314,7 +14325,7 @@
       <c r="AX216" s="1"/>
       <c r="AY216" s="1"/>
     </row>
-    <row r="217" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -14367,7 +14378,7 @@
       <c r="AX217" s="1"/>
       <c r="AY217" s="1"/>
     </row>
-    <row r="218" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -14420,7 +14431,7 @@
       <c r="AX218" s="1"/>
       <c r="AY218" s="1"/>
     </row>
-    <row r="219" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -14473,7 +14484,7 @@
       <c r="AX219" s="1"/>
       <c r="AY219" s="1"/>
     </row>
-    <row r="220" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -14526,7 +14537,7 @@
       <c r="AX220" s="1"/>
       <c r="AY220" s="1"/>
     </row>
-    <row r="221" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -14579,7 +14590,7 @@
       <c r="AX221" s="1"/>
       <c r="AY221" s="1"/>
     </row>
-    <row r="222" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -14632,7 +14643,7 @@
       <c r="AX222" s="1"/>
       <c r="AY222" s="1"/>
     </row>
-    <row r="223" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -14685,7 +14696,7 @@
       <c r="AX223" s="1"/>
       <c r="AY223" s="1"/>
     </row>
-    <row r="224" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -14738,7 +14749,7 @@
       <c r="AX224" s="1"/>
       <c r="AY224" s="1"/>
     </row>
-    <row r="225" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -14791,7 +14802,7 @@
       <c r="AX225" s="1"/>
       <c r="AY225" s="1"/>
     </row>
-    <row r="226" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -14844,7 +14855,7 @@
       <c r="AX226" s="1"/>
       <c r="AY226" s="1"/>
     </row>
-    <row r="227" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -14897,7 +14908,7 @@
       <c r="AX227" s="1"/>
       <c r="AY227" s="1"/>
     </row>
-    <row r="228" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -14950,7 +14961,7 @@
       <c r="AX228" s="1"/>
       <c r="AY228" s="1"/>
     </row>
-    <row r="229" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -15003,7 +15014,7 @@
       <c r="AX229" s="1"/>
       <c r="AY229" s="1"/>
     </row>
-    <row r="230" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -15056,7 +15067,7 @@
       <c r="AX230" s="1"/>
       <c r="AY230" s="1"/>
     </row>
-    <row r="231" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -15109,7 +15120,7 @@
       <c r="AX231" s="1"/>
       <c r="AY231" s="1"/>
     </row>
-    <row r="232" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -15162,7 +15173,7 @@
       <c r="AX232" s="1"/>
       <c r="AY232" s="1"/>
     </row>
-    <row r="233" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -15215,7 +15226,7 @@
       <c r="AX233" s="1"/>
       <c r="AY233" s="1"/>
     </row>
-    <row r="234" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -15268,7 +15279,7 @@
       <c r="AX234" s="1"/>
       <c r="AY234" s="1"/>
     </row>
-    <row r="235" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -15321,7 +15332,7 @@
       <c r="AX235" s="1"/>
       <c r="AY235" s="1"/>
     </row>
-    <row r="236" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -15374,7 +15385,7 @@
       <c r="AX236" s="1"/>
       <c r="AY236" s="1"/>
     </row>
-    <row r="237" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -15427,7 +15438,7 @@
       <c r="AX237" s="1"/>
       <c r="AY237" s="1"/>
     </row>
-    <row r="238" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -15480,7 +15491,7 @@
       <c r="AX238" s="1"/>
       <c r="AY238" s="1"/>
     </row>
-    <row r="239" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -15533,7 +15544,7 @@
       <c r="AX239" s="1"/>
       <c r="AY239" s="1"/>
     </row>
-    <row r="240" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -15586,7 +15597,7 @@
       <c r="AX240" s="1"/>
       <c r="AY240" s="1"/>
     </row>
-    <row r="241" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -15639,7 +15650,7 @@
       <c r="AX241" s="1"/>
       <c r="AY241" s="1"/>
     </row>
-    <row r="242" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -15692,7 +15703,7 @@
       <c r="AX242" s="1"/>
       <c r="AY242" s="1"/>
     </row>
-    <row r="243" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -15745,7 +15756,7 @@
       <c r="AX243" s="1"/>
       <c r="AY243" s="1"/>
     </row>
-    <row r="244" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -15798,7 +15809,7 @@
       <c r="AX244" s="1"/>
       <c r="AY244" s="1"/>
     </row>
-    <row r="245" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -15851,7 +15862,7 @@
       <c r="AX245" s="1"/>
       <c r="AY245" s="1"/>
     </row>
-    <row r="246" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -15904,7 +15915,7 @@
       <c r="AX246" s="1"/>
       <c r="AY246" s="1"/>
     </row>
-    <row r="247" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -15957,7 +15968,7 @@
       <c r="AX247" s="1"/>
       <c r="AY247" s="1"/>
     </row>
-    <row r="248" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -16010,7 +16021,7 @@
       <c r="AX248" s="1"/>
       <c r="AY248" s="1"/>
     </row>
-    <row r="249" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -16063,7 +16074,7 @@
       <c r="AX249" s="1"/>
       <c r="AY249" s="1"/>
     </row>
-    <row r="250" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -16116,7 +16127,7 @@
       <c r="AX250" s="1"/>
       <c r="AY250" s="1"/>
     </row>
-    <row r="251" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -16169,7 +16180,7 @@
       <c r="AX251" s="1"/>
       <c r="AY251" s="1"/>
     </row>
-    <row r="252" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -16222,7 +16233,7 @@
       <c r="AX252" s="1"/>
       <c r="AY252" s="1"/>
     </row>
-    <row r="253" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -16275,7 +16286,7 @@
       <c r="AX253" s="1"/>
       <c r="AY253" s="1"/>
     </row>
-    <row r="254" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -16328,7 +16339,7 @@
       <c r="AX254" s="1"/>
       <c r="AY254" s="1"/>
     </row>
-    <row r="255" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -16381,7 +16392,7 @@
       <c r="AX255" s="1"/>
       <c r="AY255" s="1"/>
     </row>
-    <row r="256" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -16434,7 +16445,7 @@
       <c r="AX256" s="1"/>
       <c r="AY256" s="1"/>
     </row>
-    <row r="257" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -16487,7 +16498,7 @@
       <c r="AX257" s="1"/>
       <c r="AY257" s="1"/>
     </row>
-    <row r="258" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -16540,7 +16551,7 @@
       <c r="AX258" s="1"/>
       <c r="AY258" s="1"/>
     </row>
-    <row r="259" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -16593,7 +16604,7 @@
       <c r="AX259" s="1"/>
       <c r="AY259" s="1"/>
     </row>
-    <row r="260" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -16646,7 +16657,7 @@
       <c r="AX260" s="1"/>
       <c r="AY260" s="1"/>
     </row>
-    <row r="261" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -16699,7 +16710,7 @@
       <c r="AX261" s="1"/>
       <c r="AY261" s="1"/>
     </row>
-    <row r="262" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -16752,7 +16763,7 @@
       <c r="AX262" s="1"/>
       <c r="AY262" s="1"/>
     </row>
-    <row r="263" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -16805,7 +16816,7 @@
       <c r="AX263" s="1"/>
       <c r="AY263" s="1"/>
     </row>
-    <row r="264" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -16858,7 +16869,7 @@
       <c r="AX264" s="1"/>
       <c r="AY264" s="1"/>
     </row>
-    <row r="265" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -16911,7 +16922,7 @@
       <c r="AX265" s="1"/>
       <c r="AY265" s="1"/>
     </row>
-    <row r="266" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -16964,7 +16975,7 @@
       <c r="AX266" s="1"/>
       <c r="AY266" s="1"/>
     </row>
-    <row r="267" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -17017,7 +17028,7 @@
       <c r="AX267" s="1"/>
       <c r="AY267" s="1"/>
     </row>
-    <row r="268" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -17070,7 +17081,7 @@
       <c r="AX268" s="1"/>
       <c r="AY268" s="1"/>
     </row>
-    <row r="269" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -17123,7 +17134,7 @@
       <c r="AX269" s="1"/>
       <c r="AY269" s="1"/>
     </row>
-    <row r="270" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -17176,7 +17187,7 @@
       <c r="AX270" s="1"/>
       <c r="AY270" s="1"/>
     </row>
-    <row r="271" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -17229,7 +17240,7 @@
       <c r="AX271" s="1"/>
       <c r="AY271" s="1"/>
     </row>
-    <row r="272" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -17282,7 +17293,7 @@
       <c r="AX272" s="1"/>
       <c r="AY272" s="1"/>
     </row>
-    <row r="273" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -17335,7 +17346,7 @@
       <c r="AX273" s="1"/>
       <c r="AY273" s="1"/>
     </row>
-    <row r="274" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -17388,7 +17399,7 @@
       <c r="AX274" s="1"/>
       <c r="AY274" s="1"/>
     </row>
-    <row r="275" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -17441,7 +17452,7 @@
       <c r="AX275" s="1"/>
       <c r="AY275" s="1"/>
     </row>
-    <row r="276" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -17494,7 +17505,7 @@
       <c r="AX276" s="1"/>
       <c r="AY276" s="1"/>
     </row>
-    <row r="277" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -17547,7 +17558,7 @@
       <c r="AX277" s="1"/>
       <c r="AY277" s="1"/>
     </row>
-    <row r="278" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -17600,7 +17611,7 @@
       <c r="AX278" s="1"/>
       <c r="AY278" s="1"/>
     </row>
-    <row r="279" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -17653,7 +17664,7 @@
       <c r="AX279" s="1"/>
       <c r="AY279" s="1"/>
     </row>
-    <row r="280" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -17706,7 +17717,7 @@
       <c r="AX280" s="1"/>
       <c r="AY280" s="1"/>
     </row>
-    <row r="281" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -17759,7 +17770,7 @@
       <c r="AX281" s="1"/>
       <c r="AY281" s="1"/>
     </row>
-    <row r="282" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -17812,7 +17823,7 @@
       <c r="AX282" s="1"/>
       <c r="AY282" s="1"/>
     </row>
-    <row r="283" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -17865,7 +17876,7 @@
       <c r="AX283" s="1"/>
       <c r="AY283" s="1"/>
     </row>
-    <row r="284" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -17918,7 +17929,7 @@
       <c r="AX284" s="1"/>
       <c r="AY284" s="1"/>
     </row>
-    <row r="285" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -17971,7 +17982,7 @@
       <c r="AX285" s="1"/>
       <c r="AY285" s="1"/>
     </row>
-    <row r="286" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -18024,7 +18035,7 @@
       <c r="AX286" s="1"/>
       <c r="AY286" s="1"/>
     </row>
-    <row r="287" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -18077,7 +18088,7 @@
       <c r="AX287" s="1"/>
       <c r="AY287" s="1"/>
     </row>
-    <row r="288" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -18130,7 +18141,7 @@
       <c r="AX288" s="1"/>
       <c r="AY288" s="1"/>
     </row>
-    <row r="289" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -18183,7 +18194,7 @@
       <c r="AX289" s="1"/>
       <c r="AY289" s="1"/>
     </row>
-    <row r="290" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -18236,7 +18247,7 @@
       <c r="AX290" s="1"/>
       <c r="AY290" s="1"/>
     </row>
-    <row r="291" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -18289,7 +18300,7 @@
       <c r="AX291" s="1"/>
       <c r="AY291" s="1"/>
     </row>
-    <row r="292" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -18342,7 +18353,7 @@
       <c r="AX292" s="1"/>
       <c r="AY292" s="1"/>
     </row>
-    <row r="293" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -18395,7 +18406,7 @@
       <c r="AX293" s="1"/>
       <c r="AY293" s="1"/>
     </row>
-    <row r="294" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -18448,7 +18459,7 @@
       <c r="AX294" s="1"/>
       <c r="AY294" s="1"/>
     </row>
-    <row r="295" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -18501,7 +18512,7 @@
       <c r="AX295" s="1"/>
       <c r="AY295" s="1"/>
     </row>
-    <row r="296" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -18554,7 +18565,7 @@
       <c r="AX296" s="1"/>
       <c r="AY296" s="1"/>
     </row>
-    <row r="297" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -18607,7 +18618,7 @@
       <c r="AX297" s="1"/>
       <c r="AY297" s="1"/>
     </row>
-    <row r="298" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -18660,7 +18671,7 @@
       <c r="AX298" s="1"/>
       <c r="AY298" s="1"/>
     </row>
-    <row r="299" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -18713,7 +18724,7 @@
       <c r="AX299" s="1"/>
       <c r="AY299" s="1"/>
     </row>
-    <row r="300" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -18766,7 +18777,7 @@
       <c r="AX300" s="1"/>
       <c r="AY300" s="1"/>
     </row>
-    <row r="301" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -18819,7 +18830,7 @@
       <c r="AX301" s="1"/>
       <c r="AY301" s="1"/>
     </row>
-    <row r="302" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -18872,7 +18883,7 @@
       <c r="AX302" s="1"/>
       <c r="AY302" s="1"/>
     </row>
-    <row r="303" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -18925,7 +18936,7 @@
       <c r="AX303" s="1"/>
       <c r="AY303" s="1"/>
     </row>
-    <row r="304" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -18978,7 +18989,7 @@
       <c r="AX304" s="1"/>
       <c r="AY304" s="1"/>
     </row>
-    <row r="305" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -19031,7 +19042,7 @@
       <c r="AX305" s="1"/>
       <c r="AY305" s="1"/>
     </row>
-    <row r="306" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -19084,7 +19095,7 @@
       <c r="AX306" s="1"/>
       <c r="AY306" s="1"/>
     </row>
-    <row r="307" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -19137,7 +19148,7 @@
       <c r="AX307" s="1"/>
       <c r="AY307" s="1"/>
     </row>
-    <row r="308" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -19190,7 +19201,7 @@
       <c r="AX308" s="1"/>
       <c r="AY308" s="1"/>
     </row>
-    <row r="309" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -19243,7 +19254,7 @@
       <c r="AX309" s="1"/>
       <c r="AY309" s="1"/>
     </row>
-    <row r="310" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -19296,7 +19307,7 @@
       <c r="AX310" s="1"/>
       <c r="AY310" s="1"/>
     </row>
-    <row r="311" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -19349,7 +19360,7 @@
       <c r="AX311" s="1"/>
       <c r="AY311" s="1"/>
     </row>
-    <row r="312" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -19402,7 +19413,7 @@
       <c r="AX312" s="1"/>
       <c r="AY312" s="1"/>
     </row>
-    <row r="313" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -19455,7 +19466,7 @@
       <c r="AX313" s="1"/>
       <c r="AY313" s="1"/>
     </row>
-    <row r="314" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -19508,7 +19519,7 @@
       <c r="AX314" s="1"/>
       <c r="AY314" s="1"/>
     </row>
-    <row r="315" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -19561,7 +19572,7 @@
       <c r="AX315" s="1"/>
       <c r="AY315" s="1"/>
     </row>
-    <row r="316" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -19614,7 +19625,7 @@
       <c r="AX316" s="1"/>
       <c r="AY316" s="1"/>
     </row>
-    <row r="317" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -19667,7 +19678,7 @@
       <c r="AX317" s="1"/>
       <c r="AY317" s="1"/>
     </row>
-    <row r="318" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -19720,7 +19731,7 @@
       <c r="AX318" s="1"/>
       <c r="AY318" s="1"/>
     </row>
-    <row r="319" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -19773,7 +19784,7 @@
       <c r="AX319" s="1"/>
       <c r="AY319" s="1"/>
     </row>
-    <row r="320" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -19826,7 +19837,7 @@
       <c r="AX320" s="1"/>
       <c r="AY320" s="1"/>
     </row>
-    <row r="321" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -19879,7 +19890,7 @@
       <c r="AX321" s="1"/>
       <c r="AY321" s="1"/>
     </row>
-    <row r="322" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -19932,7 +19943,7 @@
       <c r="AX322" s="1"/>
       <c r="AY322" s="1"/>
     </row>
-    <row r="323" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -19985,7 +19996,7 @@
       <c r="AX323" s="1"/>
       <c r="AY323" s="1"/>
     </row>
-    <row r="324" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -20038,7 +20049,7 @@
       <c r="AX324" s="1"/>
       <c r="AY324" s="1"/>
     </row>
-    <row r="325" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -20091,7 +20102,7 @@
       <c r="AX325" s="1"/>
       <c r="AY325" s="1"/>
     </row>
-    <row r="326" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -20144,7 +20155,7 @@
       <c r="AX326" s="1"/>
       <c r="AY326" s="1"/>
     </row>
-    <row r="327" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -20197,7 +20208,7 @@
       <c r="AX327" s="1"/>
       <c r="AY327" s="1"/>
     </row>
-    <row r="328" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -20250,7 +20261,7 @@
       <c r="AX328" s="1"/>
       <c r="AY328" s="1"/>
     </row>
-    <row r="329" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -20303,7 +20314,7 @@
       <c r="AX329" s="1"/>
       <c r="AY329" s="1"/>
     </row>
-    <row r="330" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -20356,7 +20367,7 @@
       <c r="AX330" s="1"/>
       <c r="AY330" s="1"/>
     </row>
-    <row r="331" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -20409,7 +20420,7 @@
       <c r="AX331" s="1"/>
       <c r="AY331" s="1"/>
     </row>
-    <row r="332" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -20462,7 +20473,7 @@
       <c r="AX332" s="1"/>
       <c r="AY332" s="1"/>
     </row>
-    <row r="333" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -20515,7 +20526,7 @@
       <c r="AX333" s="1"/>
       <c r="AY333" s="1"/>
     </row>
-    <row r="334" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -20568,7 +20579,7 @@
       <c r="AX334" s="1"/>
       <c r="AY334" s="1"/>
     </row>
-    <row r="335" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -20621,7 +20632,7 @@
       <c r="AX335" s="1"/>
       <c r="AY335" s="1"/>
     </row>
-    <row r="336" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -20674,7 +20685,7 @@
       <c r="AX336" s="1"/>
       <c r="AY336" s="1"/>
     </row>
-    <row r="337" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -20727,7 +20738,7 @@
       <c r="AX337" s="1"/>
       <c r="AY337" s="1"/>
     </row>
-    <row r="338" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -20780,7 +20791,7 @@
       <c r="AX338" s="1"/>
       <c r="AY338" s="1"/>
     </row>
-    <row r="339" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -20833,7 +20844,7 @@
       <c r="AX339" s="1"/>
       <c r="AY339" s="1"/>
     </row>
-    <row r="340" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -20886,7 +20897,7 @@
       <c r="AX340" s="1"/>
       <c r="AY340" s="1"/>
     </row>
-    <row r="341" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -20939,7 +20950,7 @@
       <c r="AX341" s="1"/>
       <c r="AY341" s="1"/>
     </row>
-    <row r="342" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -20992,7 +21003,7 @@
       <c r="AX342" s="1"/>
       <c r="AY342" s="1"/>
     </row>
-    <row r="343" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -21045,7 +21056,7 @@
       <c r="AX343" s="1"/>
       <c r="AY343" s="1"/>
     </row>
-    <row r="344" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -21098,7 +21109,7 @@
       <c r="AX344" s="1"/>
       <c r="AY344" s="1"/>
     </row>
-    <row r="345" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -21151,7 +21162,7 @@
       <c r="AX345" s="1"/>
       <c r="AY345" s="1"/>
     </row>
-    <row r="346" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -21204,7 +21215,7 @@
       <c r="AX346" s="1"/>
       <c r="AY346" s="1"/>
     </row>
-    <row r="347" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -21257,7 +21268,7 @@
       <c r="AX347" s="1"/>
       <c r="AY347" s="1"/>
     </row>
-    <row r="348" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -21310,7 +21321,7 @@
       <c r="AX348" s="1"/>
       <c r="AY348" s="1"/>
     </row>
-    <row r="349" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -21363,7 +21374,7 @@
       <c r="AX349" s="1"/>
       <c r="AY349" s="1"/>
     </row>
-    <row r="350" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -21416,7 +21427,7 @@
       <c r="AX350" s="1"/>
       <c r="AY350" s="1"/>
     </row>
-    <row r="351" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -21469,7 +21480,7 @@
       <c r="AX351" s="1"/>
       <c r="AY351" s="1"/>
     </row>
-    <row r="352" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -21522,7 +21533,7 @@
       <c r="AX352" s="1"/>
       <c r="AY352" s="1"/>
     </row>
-    <row r="353" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -21575,7 +21586,7 @@
       <c r="AX353" s="1"/>
       <c r="AY353" s="1"/>
     </row>
-    <row r="354" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -21628,7 +21639,7 @@
       <c r="AX354" s="1"/>
       <c r="AY354" s="1"/>
     </row>
-    <row r="355" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -21681,7 +21692,7 @@
       <c r="AX355" s="1"/>
       <c r="AY355" s="1"/>
     </row>
-    <row r="356" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -21734,7 +21745,7 @@
       <c r="AX356" s="1"/>
       <c r="AY356" s="1"/>
     </row>
-    <row r="357" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -21787,7 +21798,7 @@
       <c r="AX357" s="1"/>
       <c r="AY357" s="1"/>
     </row>
-    <row r="358" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -21840,7 +21851,7 @@
       <c r="AX358" s="1"/>
       <c r="AY358" s="1"/>
     </row>
-    <row r="359" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -21893,7 +21904,7 @@
       <c r="AX359" s="1"/>
       <c r="AY359" s="1"/>
     </row>
-    <row r="360" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -21946,7 +21957,7 @@
       <c r="AX360" s="1"/>
       <c r="AY360" s="1"/>
     </row>
-    <row r="361" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -21999,7 +22010,7 @@
       <c r="AX361" s="1"/>
       <c r="AY361" s="1"/>
     </row>
-    <row r="362" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -22052,7 +22063,7 @@
       <c r="AX362" s="1"/>
       <c r="AY362" s="1"/>
     </row>
-    <row r="363" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -22105,7 +22116,7 @@
       <c r="AX363" s="1"/>
       <c r="AY363" s="1"/>
     </row>
-    <row r="364" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -22158,7 +22169,7 @@
       <c r="AX364" s="1"/>
       <c r="AY364" s="1"/>
     </row>
-    <row r="365" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -22211,7 +22222,7 @@
       <c r="AX365" s="1"/>
       <c r="AY365" s="1"/>
     </row>
-    <row r="366" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -22264,7 +22275,7 @@
       <c r="AX366" s="1"/>
       <c r="AY366" s="1"/>
     </row>
-    <row r="367" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -22317,7 +22328,7 @@
       <c r="AX367" s="1"/>
       <c r="AY367" s="1"/>
     </row>
-    <row r="368" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -22370,7 +22381,7 @@
       <c r="AX368" s="1"/>
       <c r="AY368" s="1"/>
     </row>
-    <row r="369" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -22423,7 +22434,7 @@
       <c r="AX369" s="1"/>
       <c r="AY369" s="1"/>
     </row>
-    <row r="370" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -22476,7 +22487,7 @@
       <c r="AX370" s="1"/>
       <c r="AY370" s="1"/>
     </row>
-    <row r="371" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -22529,7 +22540,7 @@
       <c r="AX371" s="1"/>
       <c r="AY371" s="1"/>
     </row>
-    <row r="372" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -22582,7 +22593,7 @@
       <c r="AX372" s="1"/>
       <c r="AY372" s="1"/>
     </row>
-    <row r="373" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -22635,7 +22646,7 @@
       <c r="AX373" s="1"/>
       <c r="AY373" s="1"/>
     </row>
-    <row r="374" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -22688,7 +22699,7 @@
       <c r="AX374" s="1"/>
       <c r="AY374" s="1"/>
     </row>
-    <row r="375" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -22741,7 +22752,7 @@
       <c r="AX375" s="1"/>
       <c r="AY375" s="1"/>
     </row>
-    <row r="376" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -22794,7 +22805,7 @@
       <c r="AX376" s="1"/>
       <c r="AY376" s="1"/>
     </row>
-    <row r="377" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -22847,7 +22858,7 @@
       <c r="AX377" s="1"/>
       <c r="AY377" s="1"/>
     </row>
-    <row r="378" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -22900,7 +22911,7 @@
       <c r="AX378" s="1"/>
       <c r="AY378" s="1"/>
     </row>
-    <row r="379" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -22953,7 +22964,7 @@
       <c r="AX379" s="1"/>
       <c r="AY379" s="1"/>
     </row>
-    <row r="380" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -23006,7 +23017,7 @@
       <c r="AX380" s="1"/>
       <c r="AY380" s="1"/>
     </row>
-    <row r="381" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -23059,7 +23070,7 @@
       <c r="AX381" s="1"/>
       <c r="AY381" s="1"/>
     </row>
-    <row r="382" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -23112,7 +23123,7 @@
       <c r="AX382" s="1"/>
       <c r="AY382" s="1"/>
     </row>
-    <row r="383" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -23165,7 +23176,7 @@
       <c r="AX383" s="1"/>
       <c r="AY383" s="1"/>
     </row>
-    <row r="384" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -23218,7 +23229,7 @@
       <c r="AX384" s="1"/>
       <c r="AY384" s="1"/>
     </row>
-    <row r="385" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -23271,7 +23282,7 @@
       <c r="AX385" s="1"/>
       <c r="AY385" s="1"/>
     </row>
-    <row r="386" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -23324,7 +23335,7 @@
       <c r="AX386" s="1"/>
       <c r="AY386" s="1"/>
     </row>
-    <row r="387" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -23377,7 +23388,7 @@
       <c r="AX387" s="1"/>
       <c r="AY387" s="1"/>
     </row>
-    <row r="388" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -23430,7 +23441,7 @@
       <c r="AX388" s="1"/>
       <c r="AY388" s="1"/>
     </row>
-    <row r="389" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -23483,7 +23494,7 @@
       <c r="AX389" s="1"/>
       <c r="AY389" s="1"/>
     </row>
-    <row r="390" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -23536,7 +23547,7 @@
       <c r="AX390" s="1"/>
       <c r="AY390" s="1"/>
     </row>
-    <row r="391" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -23589,7 +23600,7 @@
       <c r="AX391" s="1"/>
       <c r="AY391" s="1"/>
     </row>
-    <row r="392" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -23642,7 +23653,7 @@
       <c r="AX392" s="1"/>
       <c r="AY392" s="1"/>
     </row>
-    <row r="393" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -23695,7 +23706,7 @@
       <c r="AX393" s="1"/>
       <c r="AY393" s="1"/>
     </row>
-    <row r="394" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -23748,7 +23759,7 @@
       <c r="AX394" s="1"/>
       <c r="AY394" s="1"/>
     </row>
-    <row r="395" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -23801,7 +23812,7 @@
       <c r="AX395" s="1"/>
       <c r="AY395" s="1"/>
     </row>
-    <row r="396" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -23854,7 +23865,7 @@
       <c r="AX396" s="1"/>
       <c r="AY396" s="1"/>
     </row>
-    <row r="397" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -23907,7 +23918,7 @@
       <c r="AX397" s="1"/>
       <c r="AY397" s="1"/>
     </row>
-    <row r="398" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -23960,7 +23971,7 @@
       <c r="AX398" s="1"/>
       <c r="AY398" s="1"/>
     </row>
-    <row r="399" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -24013,7 +24024,7 @@
       <c r="AX399" s="1"/>
       <c r="AY399" s="1"/>
     </row>
-    <row r="400" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -24066,7 +24077,7 @@
       <c r="AX400" s="1"/>
       <c r="AY400" s="1"/>
     </row>
-    <row r="401" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -24119,7 +24130,7 @@
       <c r="AX401" s="1"/>
       <c r="AY401" s="1"/>
     </row>
-    <row r="402" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -24172,7 +24183,7 @@
       <c r="AX402" s="1"/>
       <c r="AY402" s="1"/>
     </row>
-    <row r="403" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -24225,7 +24236,7 @@
       <c r="AX403" s="1"/>
       <c r="AY403" s="1"/>
     </row>
-    <row r="404" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -24278,7 +24289,7 @@
       <c r="AX404" s="1"/>
       <c r="AY404" s="1"/>
     </row>
-    <row r="405" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -24331,7 +24342,7 @@
       <c r="AX405" s="1"/>
       <c r="AY405" s="1"/>
     </row>
-    <row r="406" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -24384,7 +24395,7 @@
       <c r="AX406" s="1"/>
       <c r="AY406" s="1"/>
     </row>
-    <row r="407" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -24437,7 +24448,7 @@
       <c r="AX407" s="1"/>
       <c r="AY407" s="1"/>
     </row>
-    <row r="408" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -24490,7 +24501,7 @@
       <c r="AX408" s="1"/>
       <c r="AY408" s="1"/>
     </row>
-    <row r="409" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -24543,7 +24554,7 @@
       <c r="AX409" s="1"/>
       <c r="AY409" s="1"/>
     </row>
-    <row r="410" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -24596,7 +24607,7 @@
       <c r="AX410" s="1"/>
       <c r="AY410" s="1"/>
     </row>
-    <row r="411" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -24649,7 +24660,7 @@
       <c r="AX411" s="1"/>
       <c r="AY411" s="1"/>
     </row>
-    <row r="412" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -24702,7 +24713,7 @@
       <c r="AX412" s="1"/>
       <c r="AY412" s="1"/>
     </row>
-    <row r="413" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -24755,7 +24766,7 @@
       <c r="AX413" s="1"/>
       <c r="AY413" s="1"/>
     </row>
-    <row r="414" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -24808,7 +24819,7 @@
       <c r="AX414" s="1"/>
       <c r="AY414" s="1"/>
     </row>
-    <row r="415" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -24861,7 +24872,7 @@
       <c r="AX415" s="1"/>
       <c r="AY415" s="1"/>
     </row>
-    <row r="416" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -24914,7 +24925,7 @@
       <c r="AX416" s="1"/>
       <c r="AY416" s="1"/>
     </row>
-    <row r="417" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -24967,7 +24978,7 @@
       <c r="AX417" s="1"/>
       <c r="AY417" s="1"/>
     </row>
-    <row r="418" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -25020,7 +25031,7 @@
       <c r="AX418" s="1"/>
       <c r="AY418" s="1"/>
     </row>
-    <row r="419" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -25073,7 +25084,7 @@
       <c r="AX419" s="1"/>
       <c r="AY419" s="1"/>
     </row>
-    <row r="420" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -25126,7 +25137,7 @@
       <c r="AX420" s="1"/>
       <c r="AY420" s="1"/>
     </row>
-    <row r="421" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -25179,7 +25190,7 @@
       <c r="AX421" s="1"/>
       <c r="AY421" s="1"/>
     </row>
-    <row r="422" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -25232,7 +25243,7 @@
       <c r="AX422" s="1"/>
       <c r="AY422" s="1"/>
     </row>
-    <row r="423" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -25285,7 +25296,7 @@
       <c r="AX423" s="1"/>
       <c r="AY423" s="1"/>
     </row>
-    <row r="424" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -25338,7 +25349,7 @@
       <c r="AX424" s="1"/>
       <c r="AY424" s="1"/>
     </row>
-    <row r="425" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -25391,7 +25402,7 @@
       <c r="AX425" s="1"/>
       <c r="AY425" s="1"/>
     </row>
-    <row r="426" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -25444,7 +25455,7 @@
       <c r="AX426" s="1"/>
       <c r="AY426" s="1"/>
     </row>
-    <row r="427" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -25497,7 +25508,7 @@
       <c r="AX427" s="1"/>
       <c r="AY427" s="1"/>
     </row>
-    <row r="428" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -25550,7 +25561,7 @@
       <c r="AX428" s="1"/>
       <c r="AY428" s="1"/>
     </row>
-    <row r="429" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -25603,7 +25614,7 @@
       <c r="AX429" s="1"/>
       <c r="AY429" s="1"/>
     </row>
-    <row r="430" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -25656,7 +25667,7 @@
       <c r="AX430" s="1"/>
       <c r="AY430" s="1"/>
     </row>
-    <row r="431" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -25709,7 +25720,7 @@
       <c r="AX431" s="1"/>
       <c r="AY431" s="1"/>
     </row>
-    <row r="432" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -25762,7 +25773,7 @@
       <c r="AX432" s="1"/>
       <c r="AY432" s="1"/>
     </row>
-    <row r="433" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -25815,7 +25826,7 @@
       <c r="AX433" s="1"/>
       <c r="AY433" s="1"/>
     </row>
-    <row r="434" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -25868,7 +25879,7 @@
       <c r="AX434" s="1"/>
       <c r="AY434" s="1"/>
     </row>
-    <row r="435" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -25921,7 +25932,7 @@
       <c r="AX435" s="1"/>
       <c r="AY435" s="1"/>
     </row>
-    <row r="436" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -25974,7 +25985,7 @@
       <c r="AX436" s="1"/>
       <c r="AY436" s="1"/>
     </row>
-    <row r="437" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -26027,7 +26038,7 @@
       <c r="AX437" s="1"/>
       <c r="AY437" s="1"/>
     </row>
-    <row r="438" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -26080,7 +26091,7 @@
       <c r="AX438" s="1"/>
       <c r="AY438" s="1"/>
     </row>
-    <row r="439" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -26133,7 +26144,7 @@
       <c r="AX439" s="1"/>
       <c r="AY439" s="1"/>
     </row>
-    <row r="440" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -26186,7 +26197,7 @@
       <c r="AX440" s="1"/>
       <c r="AY440" s="1"/>
     </row>
-    <row r="441" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -26239,7 +26250,7 @@
       <c r="AX441" s="1"/>
       <c r="AY441" s="1"/>
     </row>
-    <row r="442" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -26292,7 +26303,7 @@
       <c r="AX442" s="1"/>
       <c r="AY442" s="1"/>
     </row>
-    <row r="443" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -26345,7 +26356,7 @@
       <c r="AX443" s="1"/>
       <c r="AY443" s="1"/>
     </row>
-    <row r="444" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -26398,7 +26409,7 @@
       <c r="AX444" s="1"/>
       <c r="AY444" s="1"/>
     </row>
-    <row r="445" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -26451,7 +26462,7 @@
       <c r="AX445" s="1"/>
       <c r="AY445" s="1"/>
     </row>
-    <row r="446" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -26504,7 +26515,7 @@
       <c r="AX446" s="1"/>
       <c r="AY446" s="1"/>
     </row>
-    <row r="447" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -26557,7 +26568,7 @@
       <c r="AX447" s="1"/>
       <c r="AY447" s="1"/>
     </row>
-    <row r="448" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -26610,7 +26621,7 @@
       <c r="AX448" s="1"/>
       <c r="AY448" s="1"/>
     </row>
-    <row r="449" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -26663,7 +26674,7 @@
       <c r="AX449" s="1"/>
       <c r="AY449" s="1"/>
     </row>
-    <row r="450" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -26716,7 +26727,7 @@
       <c r="AX450" s="1"/>
       <c r="AY450" s="1"/>
     </row>
-    <row r="451" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -26769,7 +26780,7 @@
       <c r="AX451" s="1"/>
       <c r="AY451" s="1"/>
     </row>
-    <row r="452" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -26822,7 +26833,7 @@
       <c r="AX452" s="1"/>
       <c r="AY452" s="1"/>
     </row>
-    <row r="453" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -26875,7 +26886,7 @@
       <c r="AX453" s="1"/>
       <c r="AY453" s="1"/>
     </row>
-    <row r="454" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -26928,7 +26939,7 @@
       <c r="AX454" s="1"/>
       <c r="AY454" s="1"/>
     </row>
-    <row r="455" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -26981,7 +26992,7 @@
       <c r="AX455" s="1"/>
       <c r="AY455" s="1"/>
     </row>
-    <row r="456" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -27034,7 +27045,7 @@
       <c r="AX456" s="1"/>
       <c r="AY456" s="1"/>
     </row>
-    <row r="457" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -27087,7 +27098,7 @@
       <c r="AX457" s="1"/>
       <c r="AY457" s="1"/>
     </row>
-    <row r="458" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -27140,7 +27151,7 @@
       <c r="AX458" s="1"/>
       <c r="AY458" s="1"/>
     </row>
-    <row r="459" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -27193,7 +27204,7 @@
       <c r="AX459" s="1"/>
       <c r="AY459" s="1"/>
     </row>
-    <row r="460" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -27246,7 +27257,7 @@
       <c r="AX460" s="1"/>
       <c r="AY460" s="1"/>
     </row>
-    <row r="461" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -27299,7 +27310,7 @@
       <c r="AX461" s="1"/>
       <c r="AY461" s="1"/>
     </row>
-    <row r="462" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -27352,7 +27363,7 @@
       <c r="AX462" s="1"/>
       <c r="AY462" s="1"/>
     </row>
-    <row r="463" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -27405,7 +27416,7 @@
       <c r="AX463" s="1"/>
       <c r="AY463" s="1"/>
     </row>
-    <row r="464" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -27458,7 +27469,7 @@
       <c r="AX464" s="1"/>
       <c r="AY464" s="1"/>
     </row>
-    <row r="465" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -27511,7 +27522,7 @@
       <c r="AX465" s="1"/>
       <c r="AY465" s="1"/>
     </row>
-    <row r="466" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -27564,7 +27575,7 @@
       <c r="AX466" s="1"/>
       <c r="AY466" s="1"/>
     </row>
-    <row r="467" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -27617,7 +27628,7 @@
       <c r="AX467" s="1"/>
       <c r="AY467" s="1"/>
     </row>
-    <row r="468" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -27670,7 +27681,7 @@
       <c r="AX468" s="1"/>
       <c r="AY468" s="1"/>
     </row>
-    <row r="469" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -27723,7 +27734,7 @@
       <c r="AX469" s="1"/>
       <c r="AY469" s="1"/>
     </row>
-    <row r="470" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -27776,7 +27787,7 @@
       <c r="AX470" s="1"/>
       <c r="AY470" s="1"/>
     </row>
-    <row r="471" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -27829,7 +27840,7 @@
       <c r="AX471" s="1"/>
       <c r="AY471" s="1"/>
     </row>
-    <row r="472" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -27882,7 +27893,7 @@
       <c r="AX472" s="1"/>
       <c r="AY472" s="1"/>
     </row>
-    <row r="473" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -27935,7 +27946,7 @@
       <c r="AX473" s="1"/>
       <c r="AY473" s="1"/>
     </row>
-    <row r="474" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -27988,7 +27999,7 @@
       <c r="AX474" s="1"/>
       <c r="AY474" s="1"/>
     </row>
-    <row r="475" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -28041,7 +28052,7 @@
       <c r="AX475" s="1"/>
       <c r="AY475" s="1"/>
     </row>
-    <row r="476" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -28094,7 +28105,7 @@
       <c r="AX476" s="1"/>
       <c r="AY476" s="1"/>
     </row>
-    <row r="477" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -28147,7 +28158,7 @@
       <c r="AX477" s="1"/>
       <c r="AY477" s="1"/>
     </row>
-    <row r="478" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -28200,7 +28211,7 @@
       <c r="AX478" s="1"/>
       <c r="AY478" s="1"/>
     </row>
-    <row r="479" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -28253,7 +28264,7 @@
       <c r="AX479" s="1"/>
       <c r="AY479" s="1"/>
     </row>
-    <row r="480" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -28306,7 +28317,7 @@
       <c r="AX480" s="1"/>
       <c r="AY480" s="1"/>
     </row>
-    <row r="481" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -28359,7 +28370,7 @@
       <c r="AX481" s="1"/>
       <c r="AY481" s="1"/>
     </row>
-    <row r="482" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -28412,7 +28423,7 @@
       <c r="AX482" s="1"/>
       <c r="AY482" s="1"/>
     </row>
-    <row r="483" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -28465,7 +28476,7 @@
       <c r="AX483" s="1"/>
       <c r="AY483" s="1"/>
     </row>
-    <row r="484" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -28518,7 +28529,7 @@
       <c r="AX484" s="1"/>
       <c r="AY484" s="1"/>
     </row>
-    <row r="485" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -28571,7 +28582,7 @@
       <c r="AX485" s="1"/>
       <c r="AY485" s="1"/>
     </row>
-    <row r="486" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -28624,7 +28635,7 @@
       <c r="AX486" s="1"/>
       <c r="AY486" s="1"/>
     </row>
-    <row r="487" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -28677,7 +28688,7 @@
       <c r="AX487" s="1"/>
       <c r="AY487" s="1"/>
     </row>
-    <row r="488" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -28730,7 +28741,7 @@
       <c r="AX488" s="1"/>
       <c r="AY488" s="1"/>
     </row>
-    <row r="489" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -28783,7 +28794,7 @@
       <c r="AX489" s="1"/>
       <c r="AY489" s="1"/>
     </row>
-    <row r="490" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -28836,7 +28847,7 @@
       <c r="AX490" s="1"/>
       <c r="AY490" s="1"/>
     </row>
-    <row r="491" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -28889,7 +28900,7 @@
       <c r="AX491" s="1"/>
       <c r="AY491" s="1"/>
     </row>
-    <row r="492" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -28942,7 +28953,7 @@
       <c r="AX492" s="1"/>
       <c r="AY492" s="1"/>
     </row>
-    <row r="493" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -28995,7 +29006,7 @@
       <c r="AX493" s="1"/>
       <c r="AY493" s="1"/>
     </row>
-    <row r="494" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -29048,7 +29059,7 @@
       <c r="AX494" s="1"/>
       <c r="AY494" s="1"/>
     </row>
-    <row r="495" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -29101,7 +29112,7 @@
       <c r="AX495" s="1"/>
       <c r="AY495" s="1"/>
     </row>
-    <row r="496" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -29154,7 +29165,7 @@
       <c r="AX496" s="1"/>
       <c r="AY496" s="1"/>
     </row>
-    <row r="497" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -29207,7 +29218,7 @@
       <c r="AX497" s="1"/>
       <c r="AY497" s="1"/>
     </row>
-    <row r="498" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -29261,7 +29272,7 @@
       <c r="AY498" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AI40"/>
+  <autoFilter ref="A3:AI40" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>